--- a/testing/dLiveChannelListTesting.xlsx
+++ b/testing/dLiveChannelListTesting.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5897" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5609" uniqueCount="615">
   <si>
     <t xml:space="preserve">Enabled</t>
   </si>
@@ -2720,7 +2720,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="129" min="129" style="3" width="35.84"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="true" ht="75.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" s="10" customFormat="true" ht="85.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3194,42 +3194,18 @@
       <c r="Z2" s="11"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="11"/>
-      <c r="AC2" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD2" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE2" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF2" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG2" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH2" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI2" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ2" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK2" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL2" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM2" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN2" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="11"/>
+      <c r="AJ2" s="11"/>
+      <c r="AK2" s="11"/>
+      <c r="AL2" s="11"/>
+      <c r="AM2" s="11"/>
+      <c r="AN2" s="11"/>
       <c r="AP2" s="11" t="s">
         <v>73</v>
       </c>
@@ -3419,51 +3395,51 @@
       <c r="DL2" s="11"/>
       <c r="DM2" s="2" t="str">
         <f aca="false">IF(AC2="x","x",IF(AC2="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DN2" s="2" t="str">
         <f aca="false">IF(AD2="x","x",IF(AD2="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DO2" s="2" t="str">
         <f aca="false">IF(AE2="x","x",IF(AE2="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DP2" s="2" t="str">
         <f aca="false">IF(AF2="x","x",IF(AF2="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DQ2" s="2" t="str">
         <f aca="false">IF(AG2="x","x",IF(AG2="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DR2" s="2" t="str">
         <f aca="false">IF(AH2="x","x",IF(AH2="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DS2" s="2" t="str">
         <f aca="false">IF(AI2="x","x",IF(AI2="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DT2" s="2" t="str">
         <f aca="false">IF(AJ2="x","x",IF(AJ2="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DU2" s="2" t="str">
         <f aca="false">IF(AK2="x","x",IF(AK2="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DV2" s="2" t="str">
         <f aca="false">IF(AL2="x","x",IF(AL2="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DW2" s="2" t="str">
         <f aca="false">IF(AM2="x","x",IF(AM2="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DX2" s="2" t="str">
         <f aca="false">IF(AN2="x","x",IF(AN2="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3522,42 +3498,18 @@
       <c r="Z3" s="11"/>
       <c r="AA3" s="11"/>
       <c r="AB3" s="11"/>
-      <c r="AC3" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD3" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE3" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF3" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG3" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH3" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI3" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ3" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK3" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL3" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM3" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN3" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="AC3" s="11"/>
+      <c r="AD3" s="11"/>
+      <c r="AE3" s="11"/>
+      <c r="AF3" s="11"/>
+      <c r="AG3" s="11"/>
+      <c r="AH3" s="11"/>
+      <c r="AI3" s="11"/>
+      <c r="AJ3" s="11"/>
+      <c r="AK3" s="11"/>
+      <c r="AL3" s="11"/>
+      <c r="AM3" s="11"/>
+      <c r="AN3" s="11"/>
       <c r="AP3" s="11" t="s">
         <v>73</v>
       </c>
@@ -3747,51 +3699,51 @@
       <c r="DL3" s="11"/>
       <c r="DM3" s="2" t="str">
         <f aca="false">IF(AC3="x","x",IF(AC3="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DN3" s="2" t="str">
         <f aca="false">IF(AD3="x","x",IF(AD3="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DO3" s="2" t="str">
         <f aca="false">IF(AE3="x","x",IF(AE3="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DP3" s="2" t="str">
         <f aca="false">IF(AF3="x","x",IF(AF3="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DQ3" s="2" t="str">
         <f aca="false">IF(AG3="x","x",IF(AG3="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DR3" s="2" t="str">
         <f aca="false">IF(AH3="x","x",IF(AH3="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DS3" s="2" t="str">
         <f aca="false">IF(AI3="x","x",IF(AI3="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DT3" s="2" t="str">
         <f aca="false">IF(AJ3="x","x",IF(AJ3="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DU3" s="2" t="str">
         <f aca="false">IF(AK3="x","x",IF(AK3="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DV3" s="2" t="str">
         <f aca="false">IF(AL3="x","x",IF(AL3="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DW3" s="2" t="str">
         <f aca="false">IF(AM3="x","x",IF(AM3="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DX3" s="2" t="str">
         <f aca="false">IF(AN3="x","x",IF(AN3="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3852,42 +3804,18 @@
       <c r="Z4" s="11"/>
       <c r="AA4" s="11"/>
       <c r="AB4" s="11"/>
-      <c r="AC4" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD4" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE4" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF4" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG4" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH4" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI4" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ4" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK4" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL4" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM4" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN4" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="AC4" s="11"/>
+      <c r="AD4" s="11"/>
+      <c r="AE4" s="11"/>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
       <c r="AP4" s="11" t="s">
         <v>73</v>
       </c>
@@ -4077,51 +4005,51 @@
       <c r="DL4" s="11"/>
       <c r="DM4" s="2" t="str">
         <f aca="false">IF(AC4="x","x",IF(AC4="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DN4" s="2" t="str">
         <f aca="false">IF(AD4="x","x",IF(AD4="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DO4" s="2" t="str">
         <f aca="false">IF(AE4="x","x",IF(AE4="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DP4" s="2" t="str">
         <f aca="false">IF(AF4="x","x",IF(AF4="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DQ4" s="2" t="str">
         <f aca="false">IF(AG4="x","x",IF(AG4="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DR4" s="2" t="str">
         <f aca="false">IF(AH4="x","x",IF(AH4="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DS4" s="2" t="str">
         <f aca="false">IF(AI4="x","x",IF(AI4="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DT4" s="2" t="str">
         <f aca="false">IF(AJ4="x","x",IF(AJ4="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DU4" s="2" t="str">
         <f aca="false">IF(AK4="x","x",IF(AK4="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DV4" s="2" t="str">
         <f aca="false">IF(AL4="x","x",IF(AL4="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DW4" s="2" t="str">
         <f aca="false">IF(AM4="x","x",IF(AM4="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DX4" s="2" t="str">
         <f aca="false">IF(AN4="x","x",IF(AN4="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4180,42 +4108,18 @@
       <c r="Z5" s="11"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="11"/>
-      <c r="AC5" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD5" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE5" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF5" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG5" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH5" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI5" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ5" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK5" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL5" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM5" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN5" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="AC5" s="11"/>
+      <c r="AD5" s="11"/>
+      <c r="AE5" s="11"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
       <c r="AP5" s="11" t="s">
         <v>73</v>
       </c>
@@ -4405,51 +4309,51 @@
       <c r="DL5" s="11"/>
       <c r="DM5" s="2" t="str">
         <f aca="false">IF(AC5="x","x",IF(AC5="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DN5" s="2" t="str">
         <f aca="false">IF(AD5="x","x",IF(AD5="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DO5" s="2" t="str">
         <f aca="false">IF(AE5="x","x",IF(AE5="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DP5" s="2" t="str">
         <f aca="false">IF(AF5="x","x",IF(AF5="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DQ5" s="2" t="str">
         <f aca="false">IF(AG5="x","x",IF(AG5="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DR5" s="2" t="str">
         <f aca="false">IF(AH5="x","x",IF(AH5="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DS5" s="2" t="str">
         <f aca="false">IF(AI5="x","x",IF(AI5="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DT5" s="2" t="str">
         <f aca="false">IF(AJ5="x","x",IF(AJ5="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DU5" s="2" t="str">
         <f aca="false">IF(AK5="x","x",IF(AK5="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DV5" s="2" t="str">
         <f aca="false">IF(AL5="x","x",IF(AL5="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DW5" s="2" t="str">
         <f aca="false">IF(AM5="x","x",IF(AM5="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DX5" s="2" t="str">
         <f aca="false">IF(AN5="x","x",IF(AN5="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4510,42 +4414,18 @@
       <c r="Z6" s="11"/>
       <c r="AA6" s="11"/>
       <c r="AB6" s="11"/>
-      <c r="AC6" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD6" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE6" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF6" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG6" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH6" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI6" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ6" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK6" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL6" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM6" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN6" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="AC6" s="11"/>
+      <c r="AD6" s="11"/>
+      <c r="AE6" s="11"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
       <c r="AP6" s="11" t="s">
         <v>73</v>
       </c>
@@ -4735,51 +4615,51 @@
       <c r="DL6" s="11"/>
       <c r="DM6" s="2" t="str">
         <f aca="false">IF(AC6="x","x",IF(AC6="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DN6" s="2" t="str">
         <f aca="false">IF(AD6="x","x",IF(AD6="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DO6" s="2" t="str">
         <f aca="false">IF(AE6="x","x",IF(AE6="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DP6" s="2" t="str">
         <f aca="false">IF(AF6="x","x",IF(AF6="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DQ6" s="2" t="str">
         <f aca="false">IF(AG6="x","x",IF(AG6="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DR6" s="2" t="str">
         <f aca="false">IF(AH6="x","x",IF(AH6="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DS6" s="2" t="str">
         <f aca="false">IF(AI6="x","x",IF(AI6="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DT6" s="2" t="str">
         <f aca="false">IF(AJ6="x","x",IF(AJ6="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DU6" s="2" t="str">
         <f aca="false">IF(AK6="x","x",IF(AK6="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DV6" s="2" t="str">
         <f aca="false">IF(AL6="x","x",IF(AL6="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DW6" s="2" t="str">
         <f aca="false">IF(AM6="x","x",IF(AM6="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DX6" s="2" t="str">
         <f aca="false">IF(AN6="x","x",IF(AN6="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4838,42 +4718,18 @@
       <c r="Z7" s="11"/>
       <c r="AA7" s="11"/>
       <c r="AB7" s="11"/>
-      <c r="AC7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN7" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="AC7" s="11"/>
+      <c r="AD7" s="11"/>
+      <c r="AE7" s="11"/>
+      <c r="AF7" s="11"/>
+      <c r="AG7" s="11"/>
+      <c r="AH7" s="11"/>
+      <c r="AI7" s="11"/>
+      <c r="AJ7" s="11"/>
+      <c r="AK7" s="11"/>
+      <c r="AL7" s="11"/>
+      <c r="AM7" s="11"/>
+      <c r="AN7" s="11"/>
       <c r="AP7" s="11" t="s">
         <v>73</v>
       </c>
@@ -5063,51 +4919,51 @@
       <c r="DL7" s="11"/>
       <c r="DM7" s="2" t="str">
         <f aca="false">IF(AC7="x","x",IF(AC7="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DN7" s="2" t="str">
         <f aca="false">IF(AD7="x","x",IF(AD7="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DO7" s="2" t="str">
         <f aca="false">IF(AE7="x","x",IF(AE7="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DP7" s="2" t="str">
         <f aca="false">IF(AF7="x","x",IF(AF7="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DQ7" s="2" t="str">
         <f aca="false">IF(AG7="x","x",IF(AG7="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DR7" s="2" t="str">
         <f aca="false">IF(AH7="x","x",IF(AH7="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DS7" s="2" t="str">
         <f aca="false">IF(AI7="x","x",IF(AI7="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DT7" s="2" t="str">
         <f aca="false">IF(AJ7="x","x",IF(AJ7="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DU7" s="2" t="str">
         <f aca="false">IF(AK7="x","x",IF(AK7="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DV7" s="2" t="str">
         <f aca="false">IF(AL7="x","x",IF(AL7="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DW7" s="2" t="str">
         <f aca="false">IF(AM7="x","x",IF(AM7="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DX7" s="2" t="str">
         <f aca="false">IF(AN7="x","x",IF(AN7="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5168,42 +5024,18 @@
       <c r="Z8" s="11"/>
       <c r="AA8" s="11"/>
       <c r="AB8" s="11"/>
-      <c r="AC8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN8" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="AC8" s="11"/>
+      <c r="AD8" s="11"/>
+      <c r="AE8" s="11"/>
+      <c r="AF8" s="11"/>
+      <c r="AG8" s="11"/>
+      <c r="AH8" s="11"/>
+      <c r="AI8" s="11"/>
+      <c r="AJ8" s="11"/>
+      <c r="AK8" s="11"/>
+      <c r="AL8" s="11"/>
+      <c r="AM8" s="11"/>
+      <c r="AN8" s="11"/>
       <c r="AP8" s="11" t="s">
         <v>73</v>
       </c>
@@ -5393,51 +5225,51 @@
       <c r="DL8" s="11"/>
       <c r="DM8" s="2" t="str">
         <f aca="false">IF(AC8="x","x",IF(AC8="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DN8" s="2" t="str">
         <f aca="false">IF(AD8="x","x",IF(AD8="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DO8" s="2" t="str">
         <f aca="false">IF(AE8="x","x",IF(AE8="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DP8" s="2" t="str">
         <f aca="false">IF(AF8="x","x",IF(AF8="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DQ8" s="2" t="str">
         <f aca="false">IF(AG8="x","x",IF(AG8="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DR8" s="2" t="str">
         <f aca="false">IF(AH8="x","x",IF(AH8="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DS8" s="2" t="str">
         <f aca="false">IF(AI8="x","x",IF(AI8="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DT8" s="2" t="str">
         <f aca="false">IF(AJ8="x","x",IF(AJ8="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DU8" s="2" t="str">
         <f aca="false">IF(AK8="x","x",IF(AK8="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DV8" s="2" t="str">
         <f aca="false">IF(AL8="x","x",IF(AL8="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DW8" s="2" t="str">
         <f aca="false">IF(AM8="x","x",IF(AM8="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DX8" s="2" t="str">
         <f aca="false">IF(AN8="x","x",IF(AN8="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5496,42 +5328,18 @@
       <c r="Z9" s="11"/>
       <c r="AA9" s="11"/>
       <c r="AB9" s="11"/>
-      <c r="AC9" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD9" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE9" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF9" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG9" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH9" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI9" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ9" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK9" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL9" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM9" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN9" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="AC9" s="11"/>
+      <c r="AD9" s="11"/>
+      <c r="AE9" s="11"/>
+      <c r="AF9" s="11"/>
+      <c r="AG9" s="11"/>
+      <c r="AH9" s="11"/>
+      <c r="AI9" s="11"/>
+      <c r="AJ9" s="11"/>
+      <c r="AK9" s="11"/>
+      <c r="AL9" s="11"/>
+      <c r="AM9" s="11"/>
+      <c r="AN9" s="11"/>
       <c r="AP9" s="11" t="s">
         <v>73</v>
       </c>
@@ -5721,51 +5529,51 @@
       <c r="DL9" s="11"/>
       <c r="DM9" s="2" t="str">
         <f aca="false">IF(AC9="x","x",IF(AC9="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DN9" s="2" t="str">
         <f aca="false">IF(AD9="x","x",IF(AD9="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DO9" s="2" t="str">
         <f aca="false">IF(AE9="x","x",IF(AE9="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DP9" s="2" t="str">
         <f aca="false">IF(AF9="x","x",IF(AF9="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DQ9" s="2" t="str">
         <f aca="false">IF(AG9="x","x",IF(AG9="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DR9" s="2" t="str">
         <f aca="false">IF(AH9="x","x",IF(AH9="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DS9" s="2" t="str">
         <f aca="false">IF(AI9="x","x",IF(AI9="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DT9" s="2" t="str">
         <f aca="false">IF(AJ9="x","x",IF(AJ9="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DU9" s="2" t="str">
         <f aca="false">IF(AK9="x","x",IF(AK9="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DV9" s="2" t="str">
         <f aca="false">IF(AL9="x","x",IF(AL9="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DW9" s="2" t="str">
         <f aca="false">IF(AM9="x","x",IF(AM9="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DX9" s="2" t="str">
         <f aca="false">IF(AN9="x","x",IF(AN9="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5826,42 +5634,18 @@
       <c r="Z10" s="11"/>
       <c r="AA10" s="11"/>
       <c r="AB10" s="11"/>
-      <c r="AC10" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD10" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE10" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF10" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG10" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH10" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI10" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ10" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK10" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL10" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM10" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN10" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="AC10" s="11"/>
+      <c r="AD10" s="11"/>
+      <c r="AE10" s="11"/>
+      <c r="AF10" s="11"/>
+      <c r="AG10" s="11"/>
+      <c r="AH10" s="11"/>
+      <c r="AI10" s="11"/>
+      <c r="AJ10" s="11"/>
+      <c r="AK10" s="11"/>
+      <c r="AL10" s="11"/>
+      <c r="AM10" s="11"/>
+      <c r="AN10" s="11"/>
       <c r="AP10" s="11" t="s">
         <v>73</v>
       </c>
@@ -6051,51 +5835,51 @@
       <c r="DL10" s="11"/>
       <c r="DM10" s="2" t="str">
         <f aca="false">IF(AC10="x","x",IF(AC10="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DN10" s="2" t="str">
         <f aca="false">IF(AD10="x","x",IF(AD10="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DO10" s="2" t="str">
         <f aca="false">IF(AE10="x","x",IF(AE10="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DP10" s="2" t="str">
         <f aca="false">IF(AF10="x","x",IF(AF10="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DQ10" s="2" t="str">
         <f aca="false">IF(AG10="x","x",IF(AG10="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DR10" s="2" t="str">
         <f aca="false">IF(AH10="x","x",IF(AH10="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DS10" s="2" t="str">
         <f aca="false">IF(AI10="x","x",IF(AI10="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DT10" s="2" t="str">
         <f aca="false">IF(AJ10="x","x",IF(AJ10="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DU10" s="2" t="str">
         <f aca="false">IF(AK10="x","x",IF(AK10="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DV10" s="2" t="str">
         <f aca="false">IF(AL10="x","x",IF(AL10="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DW10" s="2" t="str">
         <f aca="false">IF(AM10="x","x",IF(AM10="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DX10" s="2" t="str">
         <f aca="false">IF(AN10="x","x",IF(AN10="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6154,42 +5938,18 @@
       <c r="Z11" s="11"/>
       <c r="AA11" s="11"/>
       <c r="AB11" s="11"/>
-      <c r="AC11" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD11" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE11" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF11" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG11" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH11" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI11" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ11" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK11" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL11" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM11" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN11" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="AC11" s="11"/>
+      <c r="AD11" s="11"/>
+      <c r="AE11" s="11"/>
+      <c r="AF11" s="11"/>
+      <c r="AG11" s="11"/>
+      <c r="AH11" s="11"/>
+      <c r="AI11" s="11"/>
+      <c r="AJ11" s="11"/>
+      <c r="AK11" s="11"/>
+      <c r="AL11" s="11"/>
+      <c r="AM11" s="11"/>
+      <c r="AN11" s="11"/>
       <c r="AP11" s="11" t="s">
         <v>73</v>
       </c>
@@ -6379,51 +6139,51 @@
       <c r="DL11" s="11"/>
       <c r="DM11" s="2" t="str">
         <f aca="false">IF(AC11="x","x",IF(AC11="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DN11" s="2" t="str">
         <f aca="false">IF(AD11="x","x",IF(AD11="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DO11" s="2" t="str">
         <f aca="false">IF(AE11="x","x",IF(AE11="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DP11" s="2" t="str">
         <f aca="false">IF(AF11="x","x",IF(AF11="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DQ11" s="2" t="str">
         <f aca="false">IF(AG11="x","x",IF(AG11="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DR11" s="2" t="str">
         <f aca="false">IF(AH11="x","x",IF(AH11="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DS11" s="2" t="str">
         <f aca="false">IF(AI11="x","x",IF(AI11="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DT11" s="2" t="str">
         <f aca="false">IF(AJ11="x","x",IF(AJ11="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DU11" s="2" t="str">
         <f aca="false">IF(AK11="x","x",IF(AK11="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DV11" s="2" t="str">
         <f aca="false">IF(AL11="x","x",IF(AL11="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DW11" s="2" t="str">
         <f aca="false">IF(AM11="x","x",IF(AM11="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DX11" s="2" t="str">
         <f aca="false">IF(AN11="x","x",IF(AN11="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6484,42 +6244,18 @@
       </c>
       <c r="AA12" s="11"/>
       <c r="AB12" s="11"/>
-      <c r="AC12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN12" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="AC12" s="11"/>
+      <c r="AD12" s="11"/>
+      <c r="AE12" s="11"/>
+      <c r="AF12" s="11"/>
+      <c r="AG12" s="11"/>
+      <c r="AH12" s="11"/>
+      <c r="AI12" s="11"/>
+      <c r="AJ12" s="11"/>
+      <c r="AK12" s="11"/>
+      <c r="AL12" s="11"/>
+      <c r="AM12" s="11"/>
+      <c r="AN12" s="11"/>
       <c r="AP12" s="11" t="s">
         <v>73</v>
       </c>
@@ -6709,51 +6445,51 @@
       <c r="DL12" s="11"/>
       <c r="DM12" s="2" t="str">
         <f aca="false">IF(AC12="x","x",IF(AC12="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DN12" s="2" t="str">
         <f aca="false">IF(AD12="x","x",IF(AD12="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DO12" s="2" t="str">
         <f aca="false">IF(AE12="x","x",IF(AE12="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DP12" s="2" t="str">
         <f aca="false">IF(AF12="x","x",IF(AF12="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DQ12" s="2" t="str">
         <f aca="false">IF(AG12="x","x",IF(AG12="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DR12" s="2" t="str">
         <f aca="false">IF(AH12="x","x",IF(AH12="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DS12" s="2" t="str">
         <f aca="false">IF(AI12="x","x",IF(AI12="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DT12" s="2" t="str">
         <f aca="false">IF(AJ12="x","x",IF(AJ12="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DU12" s="2" t="str">
         <f aca="false">IF(AK12="x","x",IF(AK12="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DV12" s="2" t="str">
         <f aca="false">IF(AL12="x","x",IF(AL12="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DW12" s="2" t="str">
         <f aca="false">IF(AM12="x","x",IF(AM12="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DX12" s="2" t="str">
         <f aca="false">IF(AN12="x","x",IF(AN12="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6812,42 +6548,18 @@
         <v>79</v>
       </c>
       <c r="AB13" s="11"/>
-      <c r="AC13" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD13" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE13" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF13" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG13" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH13" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI13" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ13" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK13" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL13" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM13" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN13" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="AC13" s="11"/>
+      <c r="AD13" s="11"/>
+      <c r="AE13" s="11"/>
+      <c r="AF13" s="11"/>
+      <c r="AG13" s="11"/>
+      <c r="AH13" s="11"/>
+      <c r="AI13" s="11"/>
+      <c r="AJ13" s="11"/>
+      <c r="AK13" s="11"/>
+      <c r="AL13" s="11"/>
+      <c r="AM13" s="11"/>
+      <c r="AN13" s="11"/>
       <c r="AP13" s="11" t="s">
         <v>73</v>
       </c>
@@ -7037,51 +6749,51 @@
       <c r="DL13" s="11"/>
       <c r="DM13" s="2" t="str">
         <f aca="false">IF(AC13="x","x",IF(AC13="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DN13" s="2" t="str">
         <f aca="false">IF(AD13="x","x",IF(AD13="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DO13" s="2" t="str">
         <f aca="false">IF(AE13="x","x",IF(AE13="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DP13" s="2" t="str">
         <f aca="false">IF(AF13="x","x",IF(AF13="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DQ13" s="2" t="str">
         <f aca="false">IF(AG13="x","x",IF(AG13="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DR13" s="2" t="str">
         <f aca="false">IF(AH13="x","x",IF(AH13="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DS13" s="2" t="str">
         <f aca="false">IF(AI13="x","x",IF(AI13="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DT13" s="2" t="str">
         <f aca="false">IF(AJ13="x","x",IF(AJ13="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DU13" s="2" t="str">
         <f aca="false">IF(AK13="x","x",IF(AK13="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DV13" s="2" t="str">
         <f aca="false">IF(AL13="x","x",IF(AL13="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DW13" s="2" t="str">
         <f aca="false">IF(AM13="x","x",IF(AM13="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DX13" s="2" t="str">
         <f aca="false">IF(AN13="x","x",IF(AN13="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7121,42 +6833,18 @@
       <c r="N14" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="P14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="R14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="S14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="T14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="U14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="V14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="W14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="X14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA14" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
+      <c r="X14" s="11"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="11"/>
+      <c r="AA14" s="11"/>
       <c r="AB14" s="11"/>
       <c r="AC14" s="11" t="s">
         <v>79</v>
@@ -7312,51 +7000,51 @@
       </c>
       <c r="CZ14" s="2" t="str">
         <f aca="false">IF(P14="x","x",IF(P14="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DA14" s="2" t="str">
         <f aca="false">IF(Q14="x","x",IF(Q14="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DB14" s="2" t="str">
         <f aca="false">IF(R14="x","x",IF(R14="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DC14" s="2" t="str">
         <f aca="false">IF(S14="x","x",IF(S14="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DD14" s="2" t="str">
         <f aca="false">IF(T14="x","x",IF(T14="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DE14" s="2" t="str">
         <f aca="false">IF(U14="x","x",IF(U14="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DF14" s="2" t="str">
         <f aca="false">IF(V14="x","x",IF(V14="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DG14" s="2" t="str">
         <f aca="false">IF(W14="x","x",IF(W14="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DH14" s="2" t="str">
         <f aca="false">IF(X14="x","x",IF(X14="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DI14" s="2" t="str">
         <f aca="false">IF(Y14="x","x",IF(Y14="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DJ14" s="2" t="str">
         <f aca="false">IF(Z14="x","x",IF(Z14="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DK14" s="2" t="str">
         <f aca="false">IF(AA14="x","x",IF(AA14="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DL14" s="11"/>
       <c r="DM14" s="2" t="str">
@@ -7451,42 +7139,18 @@
       <c r="N15" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="P15" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q15" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="R15" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="S15" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="T15" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="U15" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="V15" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="W15" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="X15" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y15" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z15" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA15" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="11"/>
+      <c r="AA15" s="11"/>
       <c r="AB15" s="11"/>
       <c r="AC15" s="11"/>
       <c r="AD15" s="11" t="s">
@@ -7642,51 +7306,51 @@
       </c>
       <c r="CZ15" s="2" t="str">
         <f aca="false">IF(P15="x","x",IF(P15="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DA15" s="2" t="str">
         <f aca="false">IF(Q15="x","x",IF(Q15="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DB15" s="2" t="str">
         <f aca="false">IF(R15="x","x",IF(R15="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DC15" s="2" t="str">
         <f aca="false">IF(S15="x","x",IF(S15="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DD15" s="2" t="str">
         <f aca="false">IF(T15="x","x",IF(T15="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DE15" s="2" t="str">
         <f aca="false">IF(U15="x","x",IF(U15="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DF15" s="2" t="str">
         <f aca="false">IF(V15="x","x",IF(V15="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DG15" s="2" t="str">
         <f aca="false">IF(W15="x","x",IF(W15="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DH15" s="2" t="str">
         <f aca="false">IF(X15="x","x",IF(X15="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DI15" s="2" t="str">
         <f aca="false">IF(Y15="x","x",IF(Y15="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DJ15" s="2" t="str">
         <f aca="false">IF(Z15="x","x",IF(Z15="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DK15" s="2" t="str">
         <f aca="false">IF(AA15="x","x",IF(AA15="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DL15" s="11"/>
       <c r="DM15" s="2" t="str">
@@ -7781,42 +7445,18 @@
       <c r="N16" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="P16" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q16" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="R16" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="S16" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="T16" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="U16" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="V16" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="W16" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="X16" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y16" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z16" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA16" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
+      <c r="AA16" s="11"/>
       <c r="AB16" s="11"/>
       <c r="AC16" s="11"/>
       <c r="AD16" s="11"/>
@@ -7972,51 +7612,51 @@
       </c>
       <c r="CZ16" s="2" t="str">
         <f aca="false">IF(P16="x","x",IF(P16="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DA16" s="2" t="str">
         <f aca="false">IF(Q16="x","x",IF(Q16="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DB16" s="2" t="str">
         <f aca="false">IF(R16="x","x",IF(R16="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DC16" s="2" t="str">
         <f aca="false">IF(S16="x","x",IF(S16="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DD16" s="2" t="str">
         <f aca="false">IF(T16="x","x",IF(T16="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DE16" s="2" t="str">
         <f aca="false">IF(U16="x","x",IF(U16="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DF16" s="2" t="str">
         <f aca="false">IF(V16="x","x",IF(V16="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DG16" s="2" t="str">
         <f aca="false">IF(W16="x","x",IF(W16="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DH16" s="2" t="str">
         <f aca="false">IF(X16="x","x",IF(X16="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DI16" s="2" t="str">
         <f aca="false">IF(Y16="x","x",IF(Y16="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DJ16" s="2" t="str">
         <f aca="false">IF(Z16="x","x",IF(Z16="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DK16" s="2" t="str">
         <f aca="false">IF(AA16="x","x",IF(AA16="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DL16" s="11"/>
       <c r="DM16" s="2" t="str">
@@ -8111,42 +7751,18 @@
       <c r="N17" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="P17" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q17" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="R17" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="S17" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="T17" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="U17" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="V17" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="W17" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="X17" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y17" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z17" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA17" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="11"/>
+      <c r="W17" s="11"/>
+      <c r="X17" s="11"/>
+      <c r="Y17" s="11"/>
+      <c r="Z17" s="11"/>
+      <c r="AA17" s="11"/>
       <c r="AB17" s="11"/>
       <c r="AC17" s="11"/>
       <c r="AD17" s="11"/>
@@ -8302,51 +7918,51 @@
       </c>
       <c r="CZ17" s="2" t="str">
         <f aca="false">IF(P17="x","x",IF(P17="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DA17" s="2" t="str">
         <f aca="false">IF(Q17="x","x",IF(Q17="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DB17" s="2" t="str">
         <f aca="false">IF(R17="x","x",IF(R17="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DC17" s="2" t="str">
         <f aca="false">IF(S17="x","x",IF(S17="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DD17" s="2" t="str">
         <f aca="false">IF(T17="x","x",IF(T17="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DE17" s="2" t="str">
         <f aca="false">IF(U17="x","x",IF(U17="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DF17" s="2" t="str">
         <f aca="false">IF(V17="x","x",IF(V17="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DG17" s="2" t="str">
         <f aca="false">IF(W17="x","x",IF(W17="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DH17" s="2" t="str">
         <f aca="false">IF(X17="x","x",IF(X17="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DI17" s="2" t="str">
         <f aca="false">IF(Y17="x","x",IF(Y17="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DJ17" s="2" t="str">
         <f aca="false">IF(Z17="x","x",IF(Z17="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DK17" s="2" t="str">
         <f aca="false">IF(AA17="x","x",IF(AA17="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DL17" s="11"/>
       <c r="DM17" s="2" t="str">
@@ -8441,42 +8057,18 @@
       <c r="N18" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="P18" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q18" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="R18" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="S18" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="T18" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="U18" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="V18" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="W18" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="X18" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y18" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z18" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA18" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
+      <c r="V18" s="11"/>
+      <c r="W18" s="11"/>
+      <c r="X18" s="11"/>
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="11"/>
+      <c r="AA18" s="11"/>
       <c r="AB18" s="11"/>
       <c r="AC18" s="11"/>
       <c r="AD18" s="11"/>
@@ -8632,51 +8224,51 @@
       </c>
       <c r="CZ18" s="2" t="str">
         <f aca="false">IF(P18="x","x",IF(P18="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DA18" s="2" t="str">
         <f aca="false">IF(Q18="x","x",IF(Q18="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DB18" s="2" t="str">
         <f aca="false">IF(R18="x","x",IF(R18="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DC18" s="2" t="str">
         <f aca="false">IF(S18="x","x",IF(S18="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DD18" s="2" t="str">
         <f aca="false">IF(T18="x","x",IF(T18="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DE18" s="2" t="str">
         <f aca="false">IF(U18="x","x",IF(U18="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DF18" s="2" t="str">
         <f aca="false">IF(V18="x","x",IF(V18="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DG18" s="2" t="str">
         <f aca="false">IF(W18="x","x",IF(W18="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DH18" s="2" t="str">
         <f aca="false">IF(X18="x","x",IF(X18="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DI18" s="2" t="str">
         <f aca="false">IF(Y18="x","x",IF(Y18="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DJ18" s="2" t="str">
         <f aca="false">IF(Z18="x","x",IF(Z18="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DK18" s="2" t="str">
         <f aca="false">IF(AA18="x","x",IF(AA18="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DL18" s="11"/>
       <c r="DM18" s="2" t="str">
@@ -8771,42 +8363,18 @@
       <c r="N19" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="P19" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q19" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="R19" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="S19" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="T19" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="U19" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="V19" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="W19" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="X19" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y19" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z19" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA19" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
+      <c r="T19" s="11"/>
+      <c r="U19" s="11"/>
+      <c r="V19" s="11"/>
+      <c r="W19" s="11"/>
+      <c r="X19" s="11"/>
+      <c r="Y19" s="11"/>
+      <c r="Z19" s="11"/>
+      <c r="AA19" s="11"/>
       <c r="AB19" s="11"/>
       <c r="AC19" s="11"/>
       <c r="AD19" s="11"/>
@@ -8962,51 +8530,51 @@
       </c>
       <c r="CZ19" s="2" t="str">
         <f aca="false">IF(P19="x","x",IF(P19="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DA19" s="2" t="str">
         <f aca="false">IF(Q19="x","x",IF(Q19="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DB19" s="2" t="str">
         <f aca="false">IF(R19="x","x",IF(R19="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DC19" s="2" t="str">
         <f aca="false">IF(S19="x","x",IF(S19="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DD19" s="2" t="str">
         <f aca="false">IF(T19="x","x",IF(T19="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DE19" s="2" t="str">
         <f aca="false">IF(U19="x","x",IF(U19="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DF19" s="2" t="str">
         <f aca="false">IF(V19="x","x",IF(V19="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DG19" s="2" t="str">
         <f aca="false">IF(W19="x","x",IF(W19="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DH19" s="2" t="str">
         <f aca="false">IF(X19="x","x",IF(X19="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DI19" s="2" t="str">
         <f aca="false">IF(Y19="x","x",IF(Y19="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DJ19" s="2" t="str">
         <f aca="false">IF(Z19="x","x",IF(Z19="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DK19" s="2" t="str">
         <f aca="false">IF(AA19="x","x",IF(AA19="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DL19" s="11"/>
       <c r="DM19" s="2" t="str">
@@ -9101,42 +8669,18 @@
       <c r="N20" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="P20" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q20" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="R20" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="S20" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="T20" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="U20" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="V20" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="W20" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="X20" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y20" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z20" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA20" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+      <c r="T20" s="11"/>
+      <c r="U20" s="11"/>
+      <c r="V20" s="11"/>
+      <c r="W20" s="11"/>
+      <c r="X20" s="11"/>
+      <c r="Y20" s="11"/>
+      <c r="Z20" s="11"/>
+      <c r="AA20" s="11"/>
       <c r="AB20" s="11"/>
       <c r="AC20" s="11"/>
       <c r="AD20" s="11"/>
@@ -9292,51 +8836,51 @@
       </c>
       <c r="CZ20" s="2" t="str">
         <f aca="false">IF(P20="x","x",IF(P20="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DA20" s="2" t="str">
         <f aca="false">IF(Q20="x","x",IF(Q20="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DB20" s="2" t="str">
         <f aca="false">IF(R20="x","x",IF(R20="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DC20" s="2" t="str">
         <f aca="false">IF(S20="x","x",IF(S20="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DD20" s="2" t="str">
         <f aca="false">IF(T20="x","x",IF(T20="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DE20" s="2" t="str">
         <f aca="false">IF(U20="x","x",IF(U20="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DF20" s="2" t="str">
         <f aca="false">IF(V20="x","x",IF(V20="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DG20" s="2" t="str">
         <f aca="false">IF(W20="x","x",IF(W20="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DH20" s="2" t="str">
         <f aca="false">IF(X20="x","x",IF(X20="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DI20" s="2" t="str">
         <f aca="false">IF(Y20="x","x",IF(Y20="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DJ20" s="2" t="str">
         <f aca="false">IF(Z20="x","x",IF(Z20="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DK20" s="2" t="str">
         <f aca="false">IF(AA20="x","x",IF(AA20="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DL20" s="11"/>
       <c r="DM20" s="2" t="str">
@@ -9431,42 +8975,18 @@
       <c r="N21" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="P21" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q21" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="R21" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="S21" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="T21" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="U21" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="V21" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="W21" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="X21" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y21" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z21" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA21" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="11"/>
+      <c r="T21" s="11"/>
+      <c r="U21" s="11"/>
+      <c r="V21" s="11"/>
+      <c r="W21" s="11"/>
+      <c r="X21" s="11"/>
+      <c r="Y21" s="11"/>
+      <c r="Z21" s="11"/>
+      <c r="AA21" s="11"/>
       <c r="AB21" s="11"/>
       <c r="AC21" s="11"/>
       <c r="AD21" s="11"/>
@@ -9622,51 +9142,51 @@
       </c>
       <c r="CZ21" s="2" t="str">
         <f aca="false">IF(P21="x","x",IF(P21="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DA21" s="2" t="str">
         <f aca="false">IF(Q21="x","x",IF(Q21="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DB21" s="2" t="str">
         <f aca="false">IF(R21="x","x",IF(R21="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DC21" s="2" t="str">
         <f aca="false">IF(S21="x","x",IF(S21="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DD21" s="2" t="str">
         <f aca="false">IF(T21="x","x",IF(T21="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DE21" s="2" t="str">
         <f aca="false">IF(U21="x","x",IF(U21="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DF21" s="2" t="str">
         <f aca="false">IF(V21="x","x",IF(V21="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DG21" s="2" t="str">
         <f aca="false">IF(W21="x","x",IF(W21="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DH21" s="2" t="str">
         <f aca="false">IF(X21="x","x",IF(X21="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DI21" s="2" t="str">
         <f aca="false">IF(Y21="x","x",IF(Y21="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DJ21" s="2" t="str">
         <f aca="false">IF(Z21="x","x",IF(Z21="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DK21" s="2" t="str">
         <f aca="false">IF(AA21="x","x",IF(AA21="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DL21" s="11"/>
       <c r="DM21" s="2" t="str">
@@ -9761,42 +9281,18 @@
       <c r="N22" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="P22" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q22" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="R22" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="S22" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="T22" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="U22" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="V22" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="W22" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="X22" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y22" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z22" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA22" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="11"/>
+      <c r="Y22" s="11"/>
+      <c r="Z22" s="11"/>
+      <c r="AA22" s="11"/>
       <c r="AB22" s="11"/>
       <c r="AC22" s="11"/>
       <c r="AD22" s="11"/>
@@ -9952,51 +9448,51 @@
       </c>
       <c r="CZ22" s="2" t="str">
         <f aca="false">IF(P22="x","x",IF(P22="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DA22" s="2" t="str">
         <f aca="false">IF(Q22="x","x",IF(Q22="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DB22" s="2" t="str">
         <f aca="false">IF(R22="x","x",IF(R22="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DC22" s="2" t="str">
         <f aca="false">IF(S22="x","x",IF(S22="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DD22" s="2" t="str">
         <f aca="false">IF(T22="x","x",IF(T22="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DE22" s="2" t="str">
         <f aca="false">IF(U22="x","x",IF(U22="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DF22" s="2" t="str">
         <f aca="false">IF(V22="x","x",IF(V22="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DG22" s="2" t="str">
         <f aca="false">IF(W22="x","x",IF(W22="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DH22" s="2" t="str">
         <f aca="false">IF(X22="x","x",IF(X22="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DI22" s="2" t="str">
         <f aca="false">IF(Y22="x","x",IF(Y22="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DJ22" s="2" t="str">
         <f aca="false">IF(Z22="x","x",IF(Z22="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DK22" s="2" t="str">
         <f aca="false">IF(AA22="x","x",IF(AA22="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DL22" s="11"/>
       <c r="DM22" s="2" t="str">
@@ -10091,42 +9587,18 @@
       <c r="N23" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="P23" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q23" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="R23" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="S23" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="T23" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="U23" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="V23" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="W23" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="X23" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y23" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z23" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA23" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
+      <c r="T23" s="11"/>
+      <c r="U23" s="11"/>
+      <c r="V23" s="11"/>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+      <c r="Z23" s="11"/>
+      <c r="AA23" s="11"/>
       <c r="AB23" s="11"/>
       <c r="AC23" s="11"/>
       <c r="AD23" s="11"/>
@@ -10282,51 +9754,51 @@
       </c>
       <c r="CZ23" s="2" t="str">
         <f aca="false">IF(P23="x","x",IF(P23="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DA23" s="2" t="str">
         <f aca="false">IF(Q23="x","x",IF(Q23="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DB23" s="2" t="str">
         <f aca="false">IF(R23="x","x",IF(R23="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DC23" s="2" t="str">
         <f aca="false">IF(S23="x","x",IF(S23="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DD23" s="2" t="str">
         <f aca="false">IF(T23="x","x",IF(T23="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DE23" s="2" t="str">
         <f aca="false">IF(U23="x","x",IF(U23="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DF23" s="2" t="str">
         <f aca="false">IF(V23="x","x",IF(V23="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DG23" s="2" t="str">
         <f aca="false">IF(W23="x","x",IF(W23="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DH23" s="2" t="str">
         <f aca="false">IF(X23="x","x",IF(X23="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DI23" s="2" t="str">
         <f aca="false">IF(Y23="x","x",IF(Y23="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DJ23" s="2" t="str">
         <f aca="false">IF(Z23="x","x",IF(Z23="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DK23" s="2" t="str">
         <f aca="false">IF(AA23="x","x",IF(AA23="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DL23" s="11"/>
       <c r="DM23" s="2" t="str">
@@ -10421,42 +9893,18 @@
       <c r="N24" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="P24" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q24" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="R24" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="S24" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="T24" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="U24" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="V24" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="W24" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="X24" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y24" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z24" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA24" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="11"/>
+      <c r="V24" s="11"/>
+      <c r="W24" s="11"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="11"/>
+      <c r="Z24" s="11"/>
+      <c r="AA24" s="11"/>
       <c r="AB24" s="11"/>
       <c r="AC24" s="11"/>
       <c r="AD24" s="11"/>
@@ -10612,51 +10060,51 @@
       </c>
       <c r="CZ24" s="2" t="str">
         <f aca="false">IF(P24="x","x",IF(P24="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DA24" s="2" t="str">
         <f aca="false">IF(Q24="x","x",IF(Q24="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DB24" s="2" t="str">
         <f aca="false">IF(R24="x","x",IF(R24="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DC24" s="2" t="str">
         <f aca="false">IF(S24="x","x",IF(S24="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DD24" s="2" t="str">
         <f aca="false">IF(T24="x","x",IF(T24="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DE24" s="2" t="str">
         <f aca="false">IF(U24="x","x",IF(U24="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DF24" s="2" t="str">
         <f aca="false">IF(V24="x","x",IF(V24="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DG24" s="2" t="str">
         <f aca="false">IF(W24="x","x",IF(W24="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DH24" s="2" t="str">
         <f aca="false">IF(X24="x","x",IF(X24="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DI24" s="2" t="str">
         <f aca="false">IF(Y24="x","x",IF(Y24="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DJ24" s="2" t="str">
         <f aca="false">IF(Z24="x","x",IF(Z24="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DK24" s="2" t="str">
         <f aca="false">IF(AA24="x","x",IF(AA24="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DL24" s="11"/>
       <c r="DM24" s="2" t="str">
@@ -10751,42 +10199,18 @@
       <c r="N25" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="P25" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q25" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="R25" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="S25" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="T25" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="U25" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="V25" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="W25" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="X25" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y25" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z25" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA25" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="11"/>
+      <c r="V25" s="11"/>
+      <c r="W25" s="11"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="11"/>
+      <c r="Z25" s="11"/>
+      <c r="AA25" s="11"/>
       <c r="AB25" s="11"/>
       <c r="AC25" s="11"/>
       <c r="AD25" s="11"/>
@@ -10942,51 +10366,51 @@
       </c>
       <c r="CZ25" s="2" t="str">
         <f aca="false">IF(P25="x","x",IF(P25="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DA25" s="2" t="str">
         <f aca="false">IF(Q25="x","x",IF(Q25="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DB25" s="2" t="str">
         <f aca="false">IF(R25="x","x",IF(R25="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DC25" s="2" t="str">
         <f aca="false">IF(S25="x","x",IF(S25="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DD25" s="2" t="str">
         <f aca="false">IF(T25="x","x",IF(T25="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DE25" s="2" t="str">
         <f aca="false">IF(U25="x","x",IF(U25="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DF25" s="2" t="str">
         <f aca="false">IF(V25="x","x",IF(V25="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DG25" s="2" t="str">
         <f aca="false">IF(W25="x","x",IF(W25="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DH25" s="2" t="str">
         <f aca="false">IF(X25="x","x",IF(X25="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DI25" s="2" t="str">
         <f aca="false">IF(Y25="x","x",IF(Y25="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DJ25" s="2" t="str">
         <f aca="false">IF(Z25="x","x",IF(Z25="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DK25" s="2" t="str">
         <f aca="false">IF(AA25="x","x",IF(AA25="-","-",""))</f>
-        <v>-</v>
+        <v/>
       </c>
       <c r="DL25" s="11"/>
       <c r="DM25" s="2" t="str">

--- a/testing/dLiveChannelListTesting.xlsx
+++ b/testing/dLiveChannelListTesting.xlsx
@@ -14,9 +14,6 @@
     <sheet name="Mixer Config" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Misc" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -2440,148 +2437,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Channels"/>
-      <sheetName val="Sockets"/>
-      <sheetName val="Groups"/>
-      <sheetName val="Mixer Config"/>
-      <sheetName val="Misc"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="2">
-          <cell r="P2" t="str">
-            <v>Grp1</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="U2" t="str">
-            <v>StGrp1</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="P3" t="str">
-            <v>Grp2</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="U3" t="str">
-            <v>StGrp2</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="P4" t="str">
-            <v>Grp3</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="U4" t="str">
-            <v>StGrp3</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="P5" t="str">
-            <v>Grp4</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="U5" t="str">
-            <v>StGrp4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="P6" t="str">
-            <v>Grp5</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="U6" t="str">
-            <v>StGrp5</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="P7" t="str">
-            <v>Grp6</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="U7" t="str">
-            <v>StGrp6</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="P8" t="str">
-            <v>Grp7</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="U8" t="str">
-            <v>StGrp7</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="P9" t="str">
-            <v>Grp8</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="U9" t="str">
-            <v>StGrp8</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="P10" t="str">
-            <v>Grp9</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="U10" t="str">
-            <v>StGrp9</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="P11" t="str">
-            <v>Grp10</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="U11" t="str">
-            <v>StGrp10</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="P12" t="str">
-            <v>Grp11</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="U12" t="str">
-            <v>StGrp11</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="P13" t="str">
-            <v>Grp12</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="U13" t="str">
-            <v>StGrp12</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -2720,7 +2575,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="129" min="129" style="3" width="35.84"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="true" ht="85.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="10" customFormat="true" ht="96.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2765,100 +2620,100 @@
       </c>
       <c r="O1" s="8"/>
       <c r="P1" s="9" t="str">
-        <f aca="false">CONCATENATE("Grp1 - ",[1]Groups!P2)</f>
+        <f aca="false">CONCATENATE("Grp1 - ",Groups!P2)</f>
         <v>Grp1 - Grp1</v>
       </c>
       <c r="Q1" s="9" t="str">
-        <f aca="false">CONCATENATE("Grp2 - ",[1]Groups!P3)</f>
+        <f aca="false">CONCATENATE("Grp2 - ",Groups!P3)</f>
         <v>Grp2 - Grp2</v>
       </c>
       <c r="R1" s="9" t="str">
-        <f aca="false">CONCATENATE("Grp3 - ",[1]Groups!P4)</f>
+        <f aca="false">CONCATENATE("Grp3 - ",Groups!P4)</f>
         <v>Grp3 - Grp3</v>
       </c>
       <c r="S1" s="9" t="str">
-        <f aca="false">CONCATENATE("Grp4 - ",[1]Groups!P5)</f>
+        <f aca="false">CONCATENATE("Grp4 - ",Groups!P5)</f>
         <v>Grp4 - Grp4</v>
       </c>
       <c r="T1" s="9" t="str">
-        <f aca="false">CONCATENATE("Grp5 - ",[1]Groups!P6)</f>
+        <f aca="false">CONCATENATE("Grp5 - ",Groups!P6)</f>
         <v>Grp5 - Grp5</v>
       </c>
       <c r="U1" s="9" t="str">
-        <f aca="false">CONCATENATE("Grp6 - ",[1]Groups!P7)</f>
+        <f aca="false">CONCATENATE("Grp6 - ",Groups!P7)</f>
         <v>Grp6 - Grp6</v>
       </c>
       <c r="V1" s="9" t="str">
-        <f aca="false">CONCATENATE("Grp7 - ",[1]Groups!P8)</f>
+        <f aca="false">CONCATENATE("Grp7 - ",Groups!P8)</f>
         <v>Grp7 - Grp7</v>
       </c>
       <c r="W1" s="9" t="str">
-        <f aca="false">CONCATENATE("Grp8 - ",[1]Groups!$P9)</f>
+        <f aca="false">CONCATENATE("Grp8 - ",Groups!P9)</f>
         <v>Grp8 - Grp8</v>
       </c>
       <c r="X1" s="9" t="str">
-        <f aca="false">CONCATENATE("Grp9 - ",[1]Groups!$P10)</f>
+        <f aca="false">CONCATENATE("Grp9 - ",Groups!P10)</f>
         <v>Grp9 - Grp9</v>
       </c>
       <c r="Y1" s="9" t="str">
-        <f aca="false">CONCATENATE("Grp10 - ",[1]Groups!$P11)</f>
+        <f aca="false">CONCATENATE("Grp10 - ",Groups!P11)</f>
         <v>Grp10 - Grp10</v>
       </c>
       <c r="Z1" s="9" t="str">
-        <f aca="false">CONCATENATE("Grp11 - ",[1]Groups!$P12)</f>
+        <f aca="false">CONCATENATE("Grp11 - ",Groups!P12)</f>
         <v>Grp11 - Grp11</v>
       </c>
       <c r="AA1" s="9" t="str">
-        <f aca="false">CONCATENATE("Grp12 - ",[1]Groups!$P13)</f>
+        <f aca="false">CONCATENATE("Grp12 - ",Groups!P13)</f>
         <v>Grp12 - Grp12</v>
       </c>
       <c r="AB1" s="5"/>
       <c r="AC1" s="9" t="str">
-        <f aca="false">CONCATENATE("StGrp1 - ",[1]Groups!U2)</f>
+        <f aca="false">CONCATENATE("StGrp1 - ",Groups!U2)</f>
         <v>StGrp1 - StGrp1</v>
       </c>
       <c r="AD1" s="9" t="str">
-        <f aca="false">CONCATENATE("StGrp2 - ",[1]Groups!U3)</f>
+        <f aca="false">CONCATENATE("StGrp2 - ",Groups!U3)</f>
         <v>StGrp2 - StGrp2</v>
       </c>
       <c r="AE1" s="9" t="str">
-        <f aca="false">CONCATENATE("StGrp3 - ",[1]Groups!U4)</f>
+        <f aca="false">CONCATENATE("StGrp3 - ",Groups!U4)</f>
         <v>StGrp3 - StGrp3</v>
       </c>
       <c r="AF1" s="9" t="str">
-        <f aca="false">CONCATENATE("StGrp4 - ",[1]Groups!U5)</f>
+        <f aca="false">CONCATENATE("StGrp4 - ",Groups!U5)</f>
         <v>StGrp4 - StGrp4</v>
       </c>
       <c r="AG1" s="9" t="str">
-        <f aca="false">CONCATENATE("StGrp5 - ",[1]Groups!U6)</f>
+        <f aca="false">CONCATENATE("StGrp5 - ",Groups!U6)</f>
         <v>StGrp5 - StGrp5</v>
       </c>
       <c r="AH1" s="9" t="str">
-        <f aca="false">CONCATENATE("StGrp6 - ",[1]Groups!U7)</f>
+        <f aca="false">CONCATENATE("StGrp6 - ",Groups!U7)</f>
         <v>StGrp6 - StGrp6</v>
       </c>
       <c r="AI1" s="9" t="str">
-        <f aca="false">CONCATENATE("StGrp7 - ",[1]Groups!U8)</f>
+        <f aca="false">CONCATENATE("StGrp7 - ",Groups!U8)</f>
         <v>StGrp7 - StGrp7</v>
       </c>
       <c r="AJ1" s="9" t="str">
-        <f aca="false">CONCATENATE("StGrp8 - ",[1]Groups!U9)</f>
+        <f aca="false">CONCATENATE("StGrp8 - ",Groups!U9)</f>
         <v>StGrp8 - StGrp8</v>
       </c>
       <c r="AK1" s="9" t="str">
-        <f aca="false">CONCATENATE("StGrp9 - ",[1]Groups!U10)</f>
+        <f aca="false">CONCATENATE("StGrp9 - ",Groups!U10)</f>
         <v>StGrp9 - StGrp9</v>
       </c>
       <c r="AL1" s="9" t="str">
-        <f aca="false">CONCATENATE("StGrp10 - ",[1]Groups!U11)</f>
+        <f aca="false">CONCATENATE("StGrp10 - ",Groups!U11)</f>
         <v>StGrp10 - StGrp10</v>
       </c>
       <c r="AM1" s="9" t="str">
-        <f aca="false">CONCATENATE("StGrp11 - ",[1]Groups!U12)</f>
+        <f aca="false">CONCATENATE("StGrp11 - ",Groups!U12)</f>
         <v>StGrp11 - StGrp11</v>
       </c>
       <c r="AN1" s="9" t="str">
-        <f aca="false">CONCATENATE("StGrp12 - ",[1]Groups!U13)</f>
+        <f aca="false">CONCATENATE("StGrp12 - ",Groups!U13)</f>
         <v>StGrp12 - StGrp12</v>
       </c>
       <c r="AO1" s="8"/>
